--- a/Spark/Data/Simulated/Bruno/model_run/descriptive.xlsx
+++ b/Spark/Data/Simulated/Bruno/model_run/descriptive.xlsx
@@ -53,13 +53,13 @@
     <t xml:space="preserve">sd_persistence</t>
   </si>
   <si>
-    <t xml:space="preserve">anemo_fish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ant_NEF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ant_domacea</t>
+    <t xml:space="preserve">anemo-fish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ant-EFN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ant-domatia</t>
   </si>
   <si>
     <t xml:space="preserve">dispersal</t>
@@ -440,7 +440,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>0.432532147581255</v>
+        <v>0.432761314247921</v>
       </c>
       <c r="C2" t="n">
         <v>29.6378348128348</v>
@@ -455,25 +455,25 @@
         <v>9.73333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>8.08987037037037</v>
+        <v>8.13976388888889</v>
       </c>
       <c r="H2" t="n">
-        <v>0.114692782023116</v>
+        <v>0.114400478536747</v>
       </c>
       <c r="I2" t="n">
-        <v>21.9865091132037</v>
+        <v>21.9863818752094</v>
       </c>
       <c r="J2" t="n">
-        <v>0.102853777452261</v>
+        <v>0.102853182227786</v>
       </c>
       <c r="K2" t="n">
-        <v>18.4929325782478</v>
+        <v>18.4928255579091</v>
       </c>
       <c r="L2" t="n">
-        <v>7.19697955744444</v>
+        <v>7.19693790784743</v>
       </c>
       <c r="M2" t="n">
-        <v>7.26539189253223</v>
+        <v>7.26198331895764</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="n">
-        <v>0.379423479473726</v>
+        <v>0.380917973762537</v>
       </c>
       <c r="C3" t="n">
         <v>44.7892271883225</v>
@@ -496,25 +496,25 @@
         <v>52.3225806451613</v>
       </c>
       <c r="G3" t="n">
-        <v>39.0070161290323</v>
+        <v>39.154811827957</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0978332105758101</v>
+        <v>0.0961211208213165</v>
       </c>
       <c r="I3" t="n">
-        <v>14.6532249415342</v>
+        <v>14.653183909683</v>
       </c>
       <c r="J3" t="n">
-        <v>0.139441799022637</v>
+        <v>0.139441408558751</v>
       </c>
       <c r="K3" t="n">
-        <v>117.169604204008</v>
+        <v>117.169276106556</v>
       </c>
       <c r="L3" t="n">
-        <v>55.0711026165003</v>
+        <v>55.0709484068096</v>
       </c>
       <c r="M3" t="n">
-        <v>39.5812827068507</v>
+        <v>39.6669001432838</v>
       </c>
     </row>
     <row r="4">
@@ -522,7 +522,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.564990057042448</v>
+        <v>0.56520948353265</v>
       </c>
       <c r="C4" t="n">
         <v>17.3491044387303</v>
@@ -537,25 +537,25 @@
         <v>14.875</v>
       </c>
       <c r="G4" t="n">
-        <v>12.044609375</v>
+        <v>12.1282552083333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15384642217547</v>
+        <v>0.153953734378251</v>
       </c>
       <c r="I4" t="n">
-        <v>16.8175016202023</v>
+        <v>16.8174559995991</v>
       </c>
       <c r="J4" t="n">
-        <v>0.150806417820298</v>
+        <v>0.150806008729821</v>
       </c>
       <c r="K4" t="n">
-        <v>11.1129278668589</v>
+        <v>11.1128977209737</v>
       </c>
       <c r="L4" t="n">
-        <v>7.30905867643565</v>
+        <v>7.30903884925363</v>
       </c>
       <c r="M4" t="n">
-        <v>7.5166056052246</v>
+        <v>7.50200516269987</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +563,7 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>0.312542327160894</v>
+        <v>0.311754974947179</v>
       </c>
       <c r="C5" t="n">
         <v>54.1971600175564</v>
@@ -578,25 +578,25 @@
         <v>53.1470588235294</v>
       </c>
       <c r="G5" t="n">
-        <v>48.8960130718954</v>
+        <v>49.0234803921569</v>
       </c>
       <c r="H5" t="n">
-        <v>0.105530528322185</v>
+        <v>0.103860533363422</v>
       </c>
       <c r="I5" t="n">
-        <v>19.9193097477857</v>
+        <v>19.9192588914841</v>
       </c>
       <c r="J5" t="n">
-        <v>0.184150785091691</v>
+        <v>0.184150314933439</v>
       </c>
       <c r="K5" t="n">
-        <v>220.189236986351</v>
+        <v>220.188674817763</v>
       </c>
       <c r="L5" t="n">
-        <v>59.2023544579572</v>
+        <v>59.2022033074991</v>
       </c>
       <c r="M5" t="n">
-        <v>55.6149527518111</v>
+        <v>55.7163153962095</v>
       </c>
     </row>
     <row r="6">
@@ -604,7 +604,7 @@
         <v>17</v>
       </c>
       <c r="B6" t="n">
-        <v>0.429401209004187</v>
+        <v>0.429956698041565</v>
       </c>
       <c r="C6" t="n">
         <v>31.9950805146364</v>
@@ -619,25 +619,25 @@
         <v>93.9252873563218</v>
       </c>
       <c r="G6" t="n">
-        <v>84.0023148148148</v>
+        <v>84.3289595306513</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0883148008575894</v>
+        <v>0.0887441665300573</v>
       </c>
       <c r="I6" t="n">
-        <v>14.3685161558548</v>
+        <v>14.3685089876474</v>
       </c>
       <c r="J6" t="n">
-        <v>0.109503372925725</v>
+        <v>0.109503318296362</v>
       </c>
       <c r="K6" t="n">
-        <v>1182.08960831352</v>
+        <v>1182.08901858919</v>
       </c>
       <c r="L6" t="n">
-        <v>171.455838531837</v>
+        <v>171.455752995446</v>
       </c>
       <c r="M6" t="n">
-        <v>158.806830176628</v>
+        <v>159.199600517249</v>
       </c>
     </row>
   </sheetData>
